--- a/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0003T0006Z000C1N151_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0003T0006Z000C1N151_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>31.71093469787456</v>
+        <v>5.153026888404615</v>
       </c>
       <c r="D2" t="n">
-        <v>30.31265484971738</v>
+        <v>4.925806413079074</v>
       </c>
       <c r="E2" t="n">
-        <v>14.48645515436232</v>
+        <v>2.354048962583878</v>
       </c>
       <c r="F2" t="n">
-        <v>8.367524973313298</v>
+        <v>1.359722808163411</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>14.25526869063902</v>
+        <v>2.31648116222884</v>
       </c>
       <c r="D3" t="n">
-        <v>14.83668203674048</v>
+        <v>2.410960830970327</v>
       </c>
       <c r="E3" t="n">
-        <v>14.48645515436232</v>
+        <v>2.354048962583878</v>
       </c>
       <c r="F3" t="n">
-        <v>8.367524973313298</v>
+        <v>1.359722808163411</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>58.44844068406786</v>
+        <v>9.497871611161028</v>
       </c>
       <c r="D4" t="n">
-        <v>32.17138734112517</v>
+        <v>5.22785044293284</v>
       </c>
       <c r="E4" t="n">
-        <v>14.48645515436232</v>
+        <v>2.354048962583878</v>
       </c>
       <c r="F4" t="n">
-        <v>8.367524973313298</v>
+        <v>1.359722808163411</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>27.93389715225475</v>
+        <v>4.539258287241398</v>
       </c>
       <c r="D5" t="n">
-        <v>26.28813058945289</v>
+        <v>4.271821220786095</v>
       </c>
       <c r="E5" t="n">
-        <v>14.48645515436232</v>
+        <v>2.354048962583878</v>
       </c>
       <c r="F5" t="n">
-        <v>8.367524973313298</v>
+        <v>1.359722808163411</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>52.12863789542313</v>
+        <v>8.470903658006257</v>
       </c>
       <c r="D6" t="n">
-        <v>29.55743735249469</v>
+        <v>4.803083569780387</v>
       </c>
       <c r="E6" t="n">
-        <v>14.48645515436232</v>
+        <v>2.354048962583878</v>
       </c>
       <c r="F6" t="n">
-        <v>8.367524973313298</v>
+        <v>1.359722808163411</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>45.59750703467822</v>
+        <v>7.409594893135211</v>
       </c>
       <c r="D7" t="n">
-        <v>23.11635644303427</v>
+        <v>3.75640792199307</v>
       </c>
       <c r="E7" t="n">
-        <v>14.48645515436232</v>
+        <v>2.354048962583878</v>
       </c>
       <c r="F7" t="n">
-        <v>8.367524973313298</v>
+        <v>1.359722808163411</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>58.91923480869963</v>
+        <v>9.574375656413689</v>
       </c>
       <c r="D8" t="n">
-        <v>15.04054056283902</v>
+        <v>2.44408784146134</v>
       </c>
       <c r="E8" t="n">
-        <v>14.48645515436232</v>
+        <v>2.354048962583878</v>
       </c>
       <c r="F8" t="n">
-        <v>8.367524973313298</v>
+        <v>1.359722808163411</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>29.91049179911598</v>
+        <v>4.860454917356347</v>
       </c>
       <c r="D9" t="n">
-        <v>17.96992037847634</v>
+        <v>2.920112061502405</v>
       </c>
       <c r="E9" t="n">
-        <v>14.48645515436232</v>
+        <v>2.354048962583878</v>
       </c>
       <c r="F9" t="n">
-        <v>8.367524973313298</v>
+        <v>1.359722808163411</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>28.5496035326256</v>
+        <v>4.63931057405166</v>
       </c>
       <c r="D10" t="n">
-        <v>27.86082469602725</v>
+        <v>4.527384013104428</v>
       </c>
       <c r="E10" t="n">
-        <v>14.48645515436232</v>
+        <v>2.354048962583878</v>
       </c>
       <c r="F10" t="n">
-        <v>8.367524973313298</v>
+        <v>1.359722808163411</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>26.45014210692795</v>
+        <v>4.298148092375791</v>
       </c>
       <c r="D11" t="n">
-        <v>4.322279348379984</v>
+        <v>0.7023703941117475</v>
       </c>
       <c r="E11" t="n">
-        <v>14.48645515436232</v>
+        <v>2.354048962583878</v>
       </c>
       <c r="F11" t="n">
-        <v>8.367524973313298</v>
+        <v>1.359722808163411</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>33.3348138348257</v>
+        <v>5.416907248159176</v>
       </c>
       <c r="D12" t="n">
-        <v>16.15549442140351</v>
+        <v>2.625267843478071</v>
       </c>
       <c r="E12" t="n">
-        <v>14.48645515436232</v>
+        <v>2.354048962583878</v>
       </c>
       <c r="F12" t="n">
-        <v>8.367524973313298</v>
+        <v>1.359722808163411</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>57.5897407236541</v>
+        <v>9.358332867593791</v>
       </c>
       <c r="D13" t="n">
-        <v>17.28827967983446</v>
+        <v>2.8093454479731</v>
       </c>
       <c r="E13" t="n">
-        <v>14.48645515436232</v>
+        <v>2.354048962583878</v>
       </c>
       <c r="F13" t="n">
-        <v>8.367524973313298</v>
+        <v>1.359722808163411</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>63.62365203616076</v>
+        <v>10.33884345587613</v>
       </c>
       <c r="D14" t="n">
-        <v>17.39212194164968</v>
+        <v>2.826219815518073</v>
       </c>
       <c r="E14" t="n">
-        <v>14.48645515436232</v>
+        <v>2.354048962583878</v>
       </c>
       <c r="F14" t="n">
-        <v>8.367524973313298</v>
+        <v>1.359722808163411</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>46.00030836393983</v>
+        <v>7.475050109140223</v>
       </c>
       <c r="D15" t="n">
-        <v>3.762094057676685</v>
+        <v>0.6113402843724614</v>
       </c>
       <c r="E15" t="n">
-        <v>14.48645515436232</v>
+        <v>2.354048962583878</v>
       </c>
       <c r="F15" t="n">
-        <v>8.367524973313298</v>
+        <v>1.359722808163411</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>28.84378481090446</v>
+        <v>4.687115031771976</v>
       </c>
       <c r="D16" t="n">
-        <v>18.68154169226941</v>
+        <v>3.035750524993778</v>
       </c>
       <c r="E16" t="n">
-        <v>14.48645515436232</v>
+        <v>2.354048962583878</v>
       </c>
       <c r="F16" t="n">
-        <v>8.367524973313298</v>
+        <v>1.359722808163411</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>51.33178612622783</v>
+        <v>8.341415245512023</v>
       </c>
       <c r="D17" t="n">
-        <v>28.27204700716431</v>
+        <v>4.594207638664201</v>
       </c>
       <c r="E17" t="n">
-        <v>14.48645515436232</v>
+        <v>2.354048962583878</v>
       </c>
       <c r="F17" t="n">
-        <v>8.367524973313298</v>
+        <v>1.359722808163411</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
